--- a/events/Augsburg_2023_WC/Augsburg_2023_WC_start.xlsx
+++ b/events/Augsburg_2023_WC/Augsburg_2023_WC_start.xlsx
@@ -36579,6 +36579,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X615" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -40380,6 +40385,11 @@
       <c r="R671" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X671" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
